--- a/data/trans_camb/IP18A02-Dificultad-trans_camb.xlsx
+++ b/data/trans_camb/IP18A02-Dificultad-trans_camb.xlsx
@@ -40,7 +40,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="12">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -66,13 +66,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin"/>
-      <bottom style="thin"/>
       <diagonal/>
     </border>
     <border>
@@ -513,7 +506,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K34"/>
+  <dimension ref="A1:H34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -524,9 +517,6 @@
     <col width="14" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -542,68 +532,50 @@
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
-      <c r="E1" s="3" t="n"/>
-      <c r="F1" s="3" t="inlineStr">
+      <c r="E1" s="3" t="inlineStr">
         <is>
           <t>Niña</t>
         </is>
       </c>
-      <c r="G1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
       <c r="H1" s="3" t="n"/>
-      <c r="I1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="J1" s="3" t="n"/>
-      <c r="K1" s="3" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="4" t="n"/>
       <c r="B2" s="2" t="n"/>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>2012/2007</t>
+          <t>2016/2012</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>2016/2007</t>
+          <t>2023/2012</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>2023/2007</t>
+          <t>2016/2012</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>2012/2007</t>
+          <t>2023/2012</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>2016/2007</t>
+          <t>2016/2012</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
-          <t>2023/2007</t>
-        </is>
-      </c>
-      <c r="I2" s="3" t="inlineStr">
-        <is>
-          <t>2012/2007</t>
-        </is>
-      </c>
-      <c r="J2" s="3" t="inlineStr">
-        <is>
-          <t>2016/2007</t>
-        </is>
-      </c>
-      <c r="K2" s="3" t="inlineStr">
-        <is>
-          <t>2023/2007</t>
+          <t>2023/2012</t>
         </is>
       </c>
     </row>
@@ -616,9 +588,6 @@
       <c r="F3" s="2" t="n"/>
       <c r="G3" s="2" t="n"/>
       <c r="H3" s="2" t="n"/>
-      <c r="I3" s="2" t="n"/>
-      <c r="J3" s="2" t="n"/>
-      <c r="K3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -631,15 +600,24 @@
           <t>Cambio absoluto (puntos porcentuales)</t>
         </is>
       </c>
-      <c r="C4" s="5" t="inlineStr"/>
-      <c r="D4" s="5" t="inlineStr"/>
-      <c r="E4" s="5" t="inlineStr"/>
-      <c r="F4" s="5" t="inlineStr"/>
-      <c r="G4" s="5" t="inlineStr"/>
-      <c r="H4" s="5" t="inlineStr"/>
-      <c r="I4" s="5" t="inlineStr"/>
-      <c r="J4" s="5" t="inlineStr"/>
-      <c r="K4" s="5" t="inlineStr"/>
+      <c r="C4" s="5" t="n">
+        <v>0.1293417657978219</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>-5.106748831617261</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>-7.529373595603175</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>4.399012797078802</v>
+      </c>
+      <c r="G4" s="5" t="n">
+        <v>-3.571150797093139</v>
+      </c>
+      <c r="H4" s="5" t="n">
+        <v>-1.17583957454141</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
@@ -648,15 +626,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr"/>
-      <c r="D5" s="5" t="inlineStr"/>
-      <c r="E5" s="5" t="inlineStr"/>
-      <c r="F5" s="5" t="inlineStr"/>
-      <c r="G5" s="5" t="inlineStr"/>
-      <c r="H5" s="5" t="inlineStr"/>
-      <c r="I5" s="5" t="inlineStr"/>
-      <c r="J5" s="5" t="inlineStr"/>
-      <c r="K5" s="5" t="inlineStr"/>
+      <c r="C5" s="5" t="n">
+        <v>-5.752610764033752</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>-15.63667105934385</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>-13.23343826217409</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>-14.14761003104198</v>
+      </c>
+      <c r="G5" s="5" t="n">
+        <v>-7.686668477629559</v>
+      </c>
+      <c r="H5" s="5" t="n">
+        <v>-10.94297933448787</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n"/>
@@ -665,15 +652,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C6" s="5" t="inlineStr"/>
-      <c r="D6" s="5" t="inlineStr"/>
-      <c r="E6" s="5" t="inlineStr"/>
-      <c r="F6" s="5" t="inlineStr"/>
-      <c r="G6" s="5" t="inlineStr"/>
-      <c r="H6" s="5" t="inlineStr"/>
-      <c r="I6" s="5" t="inlineStr"/>
-      <c r="J6" s="5" t="inlineStr"/>
-      <c r="K6" s="5" t="inlineStr"/>
+      <c r="C6" s="5" t="n">
+        <v>6.05038474968315</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>9.410543889041517</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>-1.050193779142979</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>27.57735280122608</v>
+      </c>
+      <c r="G6" s="5" t="n">
+        <v>0.6987782314291822</v>
+      </c>
+      <c r="H6" s="5" t="n">
+        <v>13.73652962136018</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n"/>
@@ -682,15 +678,24 @@
           <t>Cambio relativo (%)</t>
         </is>
       </c>
-      <c r="C7" s="6" t="inlineStr"/>
-      <c r="D7" s="6" t="inlineStr"/>
-      <c r="E7" s="6" t="inlineStr"/>
-      <c r="F7" s="6" t="inlineStr"/>
-      <c r="G7" s="6" t="inlineStr"/>
-      <c r="H7" s="6" t="inlineStr"/>
-      <c r="I7" s="6" t="inlineStr"/>
-      <c r="J7" s="6" t="inlineStr"/>
-      <c r="K7" s="6" t="inlineStr"/>
+      <c r="C7" s="6" t="n">
+        <v>0.006824836292430971</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>-0.2694622618406982</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>-0.3303156433390217</v>
+      </c>
+      <c r="F7" s="6" t="n">
+        <v>0.1929858737481427</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>-0.1714166314965967</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>-0.05644075831587547</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n"/>
@@ -699,15 +704,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C8" s="6" t="inlineStr"/>
-      <c r="D8" s="6" t="inlineStr"/>
-      <c r="E8" s="6" t="inlineStr"/>
-      <c r="F8" s="6" t="inlineStr"/>
-      <c r="G8" s="6" t="inlineStr"/>
-      <c r="H8" s="6" t="inlineStr"/>
-      <c r="I8" s="6" t="inlineStr"/>
-      <c r="J8" s="6" t="inlineStr"/>
-      <c r="K8" s="6" t="inlineStr"/>
+      <c r="C8" s="6" t="n">
+        <v>-0.2641373862121611</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>-0.7567894842681909</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>-0.510950754733853</v>
+      </c>
+      <c r="F8" s="6" t="n">
+        <v>-0.5687311627629605</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>-0.3362040827973776</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>-0.5083716622079805</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
@@ -716,15 +730,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C9" s="6" t="inlineStr"/>
-      <c r="D9" s="6" t="inlineStr"/>
-      <c r="E9" s="6" t="inlineStr"/>
-      <c r="F9" s="6" t="inlineStr"/>
-      <c r="G9" s="6" t="inlineStr"/>
-      <c r="H9" s="6" t="inlineStr"/>
-      <c r="I9" s="6" t="inlineStr"/>
-      <c r="J9" s="6" t="inlineStr"/>
-      <c r="K9" s="6" t="inlineStr"/>
+      <c r="C9" s="6" t="n">
+        <v>0.4022207223595848</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>0.5965619163287513</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>-0.05497307529639448</v>
+      </c>
+      <c r="F9" s="6" t="n">
+        <v>1.267115252047603</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>0.03555931012658544</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>0.7005484488595696</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
@@ -737,15 +760,24 @@
           <t>Cambio absoluto (puntos porcentuales)</t>
         </is>
       </c>
-      <c r="C10" s="5" t="inlineStr"/>
-      <c r="D10" s="5" t="inlineStr"/>
-      <c r="E10" s="5" t="inlineStr"/>
-      <c r="F10" s="5" t="inlineStr"/>
-      <c r="G10" s="5" t="inlineStr"/>
-      <c r="H10" s="5" t="inlineStr"/>
-      <c r="I10" s="5" t="inlineStr"/>
-      <c r="J10" s="5" t="inlineStr"/>
-      <c r="K10" s="5" t="inlineStr"/>
+      <c r="C10" s="5" t="n">
+        <v>4.046811357533525</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>3.353988002259092</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>-0.9356548619937899</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>-3.473809187704602</v>
+      </c>
+      <c r="G10" s="5" t="n">
+        <v>1.617692423751418</v>
+      </c>
+      <c r="H10" s="5" t="n">
+        <v>0.003444677193742418</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
@@ -754,15 +786,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr"/>
-      <c r="D11" s="5" t="inlineStr"/>
-      <c r="E11" s="5" t="inlineStr"/>
-      <c r="F11" s="5" t="inlineStr"/>
-      <c r="G11" s="5" t="inlineStr"/>
-      <c r="H11" s="5" t="inlineStr"/>
-      <c r="I11" s="5" t="inlineStr"/>
-      <c r="J11" s="5" t="inlineStr"/>
-      <c r="K11" s="5" t="inlineStr"/>
+      <c r="C11" s="5" t="n">
+        <v>-1.828880713150869</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>-5.745364516047767</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>-7.61865986052687</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>-13.93236667707736</v>
+      </c>
+      <c r="G11" s="5" t="n">
+        <v>-2.727319509815472</v>
+      </c>
+      <c r="H11" s="5" t="n">
+        <v>-6.938398794995354</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n"/>
@@ -771,15 +812,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C12" s="5" t="inlineStr"/>
-      <c r="D12" s="5" t="inlineStr"/>
-      <c r="E12" s="5" t="inlineStr"/>
-      <c r="F12" s="5" t="inlineStr"/>
-      <c r="G12" s="5" t="inlineStr"/>
-      <c r="H12" s="5" t="inlineStr"/>
-      <c r="I12" s="5" t="inlineStr"/>
-      <c r="J12" s="5" t="inlineStr"/>
-      <c r="K12" s="5" t="inlineStr"/>
+      <c r="C12" s="5" t="n">
+        <v>10.27009614532662</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>16.52982545377025</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>5.252069961138063</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>12.61075408026074</v>
+      </c>
+      <c r="G12" s="5" t="n">
+        <v>6.291695032601921</v>
+      </c>
+      <c r="H12" s="5" t="n">
+        <v>9.73024912493503</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n"/>
@@ -788,15 +838,24 @@
           <t>Cambio relativo (%)</t>
         </is>
       </c>
-      <c r="C13" s="6" t="inlineStr"/>
-      <c r="D13" s="6" t="inlineStr"/>
-      <c r="E13" s="6" t="inlineStr"/>
-      <c r="F13" s="6" t="inlineStr"/>
-      <c r="G13" s="6" t="inlineStr"/>
-      <c r="H13" s="6" t="inlineStr"/>
-      <c r="I13" s="6" t="inlineStr"/>
-      <c r="J13" s="6" t="inlineStr"/>
-      <c r="K13" s="6" t="inlineStr"/>
+      <c r="C13" s="6" t="n">
+        <v>0.2682494644996544</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>0.2223245429687203</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>-0.04297299728671195</v>
+      </c>
+      <c r="F13" s="6" t="n">
+        <v>-0.1595460023364638</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>0.08800478756523548</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>0.0001873953788836536</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n"/>
@@ -805,15 +864,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C14" s="6" t="inlineStr"/>
-      <c r="D14" s="6" t="inlineStr"/>
-      <c r="E14" s="6" t="inlineStr"/>
-      <c r="F14" s="6" t="inlineStr"/>
-      <c r="G14" s="6" t="inlineStr"/>
-      <c r="H14" s="6" t="inlineStr"/>
-      <c r="I14" s="6" t="inlineStr"/>
-      <c r="J14" s="6" t="inlineStr"/>
-      <c r="K14" s="6" t="inlineStr"/>
+      <c r="C14" s="6" t="n">
+        <v>-0.1151429101297457</v>
+      </c>
+      <c r="D14" s="6" t="n">
+        <v>-0.3540455391694293</v>
+      </c>
+      <c r="E14" s="6" t="n">
+        <v>-0.3051460856554808</v>
+      </c>
+      <c r="F14" s="6" t="n">
+        <v>-0.6067556686313879</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>-0.135409224187347</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>-0.3649295241142991</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n"/>
@@ -822,15 +890,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C15" s="6" t="inlineStr"/>
-      <c r="D15" s="6" t="inlineStr"/>
-      <c r="E15" s="6" t="inlineStr"/>
-      <c r="F15" s="6" t="inlineStr"/>
-      <c r="G15" s="6" t="inlineStr"/>
-      <c r="H15" s="6" t="inlineStr"/>
-      <c r="I15" s="6" t="inlineStr"/>
-      <c r="J15" s="6" t="inlineStr"/>
-      <c r="K15" s="6" t="inlineStr"/>
+      <c r="C15" s="6" t="n">
+        <v>0.7960749422826305</v>
+      </c>
+      <c r="D15" s="6" t="n">
+        <v>1.265400582237111</v>
+      </c>
+      <c r="E15" s="6" t="n">
+        <v>0.2792325870425708</v>
+      </c>
+      <c r="F15" s="6" t="n">
+        <v>0.6276760015044068</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>0.3878813514878208</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>0.5653350582979447</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
@@ -843,15 +920,24 @@
           <t>Cambio absoluto (puntos porcentuales)</t>
         </is>
       </c>
-      <c r="C16" s="5" t="inlineStr"/>
-      <c r="D16" s="5" t="inlineStr"/>
-      <c r="E16" s="5" t="inlineStr"/>
-      <c r="F16" s="5" t="inlineStr"/>
-      <c r="G16" s="5" t="inlineStr"/>
-      <c r="H16" s="5" t="inlineStr"/>
-      <c r="I16" s="5" t="inlineStr"/>
-      <c r="J16" s="5" t="inlineStr"/>
-      <c r="K16" s="5" t="inlineStr"/>
+      <c r="C16" s="5" t="n">
+        <v>1.169296978830175</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>3.47644512653345</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>-0.9644694263372361</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>11.65381767488677</v>
+      </c>
+      <c r="G16" s="5" t="n">
+        <v>0.05900963690080863</v>
+      </c>
+      <c r="H16" s="5" t="n">
+        <v>6.903724001825109</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n"/>
@@ -860,15 +946,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C17" s="5" t="inlineStr"/>
-      <c r="D17" s="5" t="inlineStr"/>
-      <c r="E17" s="5" t="inlineStr"/>
-      <c r="F17" s="5" t="inlineStr"/>
-      <c r="G17" s="5" t="inlineStr"/>
-      <c r="H17" s="5" t="inlineStr"/>
-      <c r="I17" s="5" t="inlineStr"/>
-      <c r="J17" s="5" t="inlineStr"/>
-      <c r="K17" s="5" t="inlineStr"/>
+      <c r="C17" s="5" t="n">
+        <v>-7.072260350073638</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>-7.872114717719815</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>-8.851206376084564</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>-2.308979116965684</v>
+      </c>
+      <c r="G17" s="5" t="n">
+        <v>-5.613484372732651</v>
+      </c>
+      <c r="H17" s="5" t="n">
+        <v>-2.544865252707618</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n"/>
@@ -877,15 +972,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C18" s="5" t="inlineStr"/>
-      <c r="D18" s="5" t="inlineStr"/>
-      <c r="E18" s="5" t="inlineStr"/>
-      <c r="F18" s="5" t="inlineStr"/>
-      <c r="G18" s="5" t="inlineStr"/>
-      <c r="H18" s="5" t="inlineStr"/>
-      <c r="I18" s="5" t="inlineStr"/>
-      <c r="J18" s="5" t="inlineStr"/>
-      <c r="K18" s="5" t="inlineStr"/>
+      <c r="C18" s="5" t="n">
+        <v>9.566397809535818</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>18.54391152773732</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>6.898343813215835</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>28.45878179235308</v>
+      </c>
+      <c r="G18" s="5" t="n">
+        <v>5.793494313830275</v>
+      </c>
+      <c r="H18" s="5" t="n">
+        <v>17.73308139553644</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n"/>
@@ -894,15 +998,24 @@
           <t>Cambio relativo (%)</t>
         </is>
       </c>
-      <c r="C19" s="6" t="inlineStr"/>
-      <c r="D19" s="6" t="inlineStr"/>
-      <c r="E19" s="6" t="inlineStr"/>
-      <c r="F19" s="6" t="inlineStr"/>
-      <c r="G19" s="6" t="inlineStr"/>
-      <c r="H19" s="6" t="inlineStr"/>
-      <c r="I19" s="6" t="inlineStr"/>
-      <c r="J19" s="6" t="inlineStr"/>
-      <c r="K19" s="6" t="inlineStr"/>
+      <c r="C19" s="6" t="n">
+        <v>0.0526430401635324</v>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>0.1565133954297138</v>
+      </c>
+      <c r="E19" s="6" t="n">
+        <v>-0.0439144829078452</v>
+      </c>
+      <c r="F19" s="6" t="n">
+        <v>0.5306247799253864</v>
+      </c>
+      <c r="G19" s="6" t="n">
+        <v>0.002671302637918747</v>
+      </c>
+      <c r="H19" s="6" t="n">
+        <v>0.3125241419217353</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n"/>
@@ -911,15 +1024,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C20" s="6" t="inlineStr"/>
-      <c r="D20" s="6" t="inlineStr"/>
-      <c r="E20" s="6" t="inlineStr"/>
-      <c r="F20" s="6" t="inlineStr"/>
-      <c r="G20" s="6" t="inlineStr"/>
-      <c r="H20" s="6" t="inlineStr"/>
-      <c r="I20" s="6" t="inlineStr"/>
-      <c r="J20" s="6" t="inlineStr"/>
-      <c r="K20" s="6" t="inlineStr"/>
+      <c r="C20" s="6" t="n">
+        <v>-0.2767855848294636</v>
+      </c>
+      <c r="D20" s="6" t="n">
+        <v>-0.3254140426957639</v>
+      </c>
+      <c r="E20" s="6" t="n">
+        <v>-0.3497533923057579</v>
+      </c>
+      <c r="F20" s="6" t="n">
+        <v>-0.1094591277696693</v>
+      </c>
+      <c r="G20" s="6" t="n">
+        <v>-0.2232795868789786</v>
+      </c>
+      <c r="H20" s="6" t="n">
+        <v>-0.09757146217886584</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n"/>
@@ -928,15 +1050,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C21" s="6" t="inlineStr"/>
-      <c r="D21" s="6" t="inlineStr"/>
-      <c r="E21" s="6" t="inlineStr"/>
-      <c r="F21" s="6" t="inlineStr"/>
-      <c r="G21" s="6" t="inlineStr"/>
-      <c r="H21" s="6" t="inlineStr"/>
-      <c r="I21" s="6" t="inlineStr"/>
-      <c r="J21" s="6" t="inlineStr"/>
-      <c r="K21" s="6" t="inlineStr"/>
+      <c r="C21" s="6" t="n">
+        <v>0.527445105336335</v>
+      </c>
+      <c r="D21" s="6" t="n">
+        <v>0.8886512339145524</v>
+      </c>
+      <c r="E21" s="6" t="n">
+        <v>0.4032697609179278</v>
+      </c>
+      <c r="F21" s="6" t="n">
+        <v>1.491615435831322</v>
+      </c>
+      <c r="G21" s="6" t="n">
+        <v>0.2936994986739309</v>
+      </c>
+      <c r="H21" s="6" t="n">
+        <v>0.8829052906921484</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
@@ -949,15 +1080,24 @@
           <t>Cambio absoluto (puntos porcentuales)</t>
         </is>
       </c>
-      <c r="C22" s="5" t="inlineStr"/>
-      <c r="D22" s="5" t="inlineStr"/>
-      <c r="E22" s="5" t="inlineStr"/>
-      <c r="F22" s="5" t="inlineStr"/>
-      <c r="G22" s="5" t="inlineStr"/>
-      <c r="H22" s="5" t="inlineStr"/>
-      <c r="I22" s="5" t="inlineStr"/>
-      <c r="J22" s="5" t="inlineStr"/>
-      <c r="K22" s="5" t="inlineStr"/>
+      <c r="C22" s="5" t="n">
+        <v>-7.345315808214978</v>
+      </c>
+      <c r="D22" s="5" t="n">
+        <v>-8.85630486116972</v>
+      </c>
+      <c r="E22" s="5" t="n">
+        <v>6.008883172169329</v>
+      </c>
+      <c r="F22" s="5" t="n">
+        <v>-10.40213762502165</v>
+      </c>
+      <c r="G22" s="5" t="n">
+        <v>-1.486445164323358</v>
+      </c>
+      <c r="H22" s="5" t="n">
+        <v>-9.937243759977138</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="n"/>
@@ -966,15 +1106,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C23" s="5" t="inlineStr"/>
-      <c r="D23" s="5" t="inlineStr"/>
-      <c r="E23" s="5" t="inlineStr"/>
-      <c r="F23" s="5" t="inlineStr"/>
-      <c r="G23" s="5" t="inlineStr"/>
-      <c r="H23" s="5" t="inlineStr"/>
-      <c r="I23" s="5" t="inlineStr"/>
-      <c r="J23" s="5" t="inlineStr"/>
-      <c r="K23" s="5" t="inlineStr"/>
+      <c r="C23" s="5" t="n">
+        <v>-16.53926539306612</v>
+      </c>
+      <c r="D23" s="5" t="n">
+        <v>-20.7341346924839</v>
+      </c>
+      <c r="E23" s="5" t="n">
+        <v>-3.785425501635663</v>
+      </c>
+      <c r="F23" s="5" t="n">
+        <v>-19.83102232335388</v>
+      </c>
+      <c r="G23" s="5" t="n">
+        <v>-8.515694700840509</v>
+      </c>
+      <c r="H23" s="5" t="n">
+        <v>-17.51361745163727</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="n"/>
@@ -983,15 +1132,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C24" s="5" t="inlineStr"/>
-      <c r="D24" s="5" t="inlineStr"/>
-      <c r="E24" s="5" t="inlineStr"/>
-      <c r="F24" s="5" t="inlineStr"/>
-      <c r="G24" s="5" t="inlineStr"/>
-      <c r="H24" s="5" t="inlineStr"/>
-      <c r="I24" s="5" t="inlineStr"/>
-      <c r="J24" s="5" t="inlineStr"/>
-      <c r="K24" s="5" t="inlineStr"/>
+      <c r="C24" s="5" t="n">
+        <v>1.657991660681506</v>
+      </c>
+      <c r="D24" s="5" t="n">
+        <v>10.84438581925895</v>
+      </c>
+      <c r="E24" s="5" t="n">
+        <v>16.57347023623533</v>
+      </c>
+      <c r="F24" s="5" t="n">
+        <v>1.203872996351724</v>
+      </c>
+      <c r="G24" s="5" t="n">
+        <v>5.864804736013903</v>
+      </c>
+      <c r="H24" s="5" t="n">
+        <v>-0.5126497811072477</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="n"/>
@@ -1000,15 +1158,24 @@
           <t>Cambio relativo (%)</t>
         </is>
       </c>
-      <c r="C25" s="6" t="inlineStr"/>
-      <c r="D25" s="6" t="inlineStr"/>
-      <c r="E25" s="6" t="inlineStr"/>
-      <c r="F25" s="6" t="inlineStr"/>
-      <c r="G25" s="6" t="inlineStr"/>
-      <c r="H25" s="6" t="inlineStr"/>
-      <c r="I25" s="6" t="inlineStr"/>
-      <c r="J25" s="6" t="inlineStr"/>
-      <c r="K25" s="6" t="inlineStr"/>
+      <c r="C25" s="6" t="n">
+        <v>-0.3151509273361413</v>
+      </c>
+      <c r="D25" s="6" t="n">
+        <v>-0.379979944041029</v>
+      </c>
+      <c r="E25" s="6" t="n">
+        <v>0.378670420671479</v>
+      </c>
+      <c r="F25" s="6" t="n">
+        <v>-0.6555264460113503</v>
+      </c>
+      <c r="G25" s="6" t="n">
+        <v>-0.07440716333315409</v>
+      </c>
+      <c r="H25" s="6" t="n">
+        <v>-0.4974297991453772</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="n"/>
@@ -1017,15 +1184,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C26" s="6" t="inlineStr"/>
-      <c r="D26" s="6" t="inlineStr"/>
-      <c r="E26" s="6" t="inlineStr"/>
-      <c r="F26" s="6" t="inlineStr"/>
-      <c r="G26" s="6" t="inlineStr"/>
-      <c r="H26" s="6" t="inlineStr"/>
-      <c r="I26" s="6" t="inlineStr"/>
-      <c r="J26" s="6" t="inlineStr"/>
-      <c r="K26" s="6" t="inlineStr"/>
+      <c r="C26" s="6" t="n">
+        <v>-0.5979487063192366</v>
+      </c>
+      <c r="D26" s="6" t="n">
+        <v>-0.784395535815602</v>
+      </c>
+      <c r="E26" s="6" t="n">
+        <v>-0.2052223327820403</v>
+      </c>
+      <c r="F26" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="G26" s="6" t="n">
+        <v>-0.3699432281872834</v>
+      </c>
+      <c r="H26" s="6" t="n">
+        <v>-0.7931014720817212</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="n"/>
@@ -1034,15 +1210,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C27" s="6" t="inlineStr"/>
-      <c r="D27" s="6" t="inlineStr"/>
-      <c r="E27" s="6" t="inlineStr"/>
-      <c r="F27" s="6" t="inlineStr"/>
-      <c r="G27" s="6" t="inlineStr"/>
-      <c r="H27" s="6" t="inlineStr"/>
-      <c r="I27" s="6" t="inlineStr"/>
-      <c r="J27" s="6" t="inlineStr"/>
-      <c r="K27" s="6" t="inlineStr"/>
+      <c r="C27" s="6" t="n">
+        <v>0.08537553028279429</v>
+      </c>
+      <c r="D27" s="6" t="n">
+        <v>0.6136218987806529</v>
+      </c>
+      <c r="E27" s="6" t="n">
+        <v>1.437087013908857</v>
+      </c>
+      <c r="F27" s="6" t="n">
+        <v>0.3858867452920295</v>
+      </c>
+      <c r="G27" s="6" t="n">
+        <v>0.3862554403854037</v>
+      </c>
+      <c r="H27" s="6" t="n">
+        <v>-0.0235333568165607</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
@@ -1055,15 +1240,24 @@
           <t>Cambio absoluto (puntos porcentuales)</t>
         </is>
       </c>
-      <c r="C28" s="5" t="inlineStr"/>
-      <c r="D28" s="5" t="inlineStr"/>
-      <c r="E28" s="5" t="inlineStr"/>
-      <c r="F28" s="5" t="inlineStr"/>
-      <c r="G28" s="5" t="inlineStr"/>
-      <c r="H28" s="5" t="inlineStr"/>
-      <c r="I28" s="5" t="inlineStr"/>
-      <c r="J28" s="5" t="inlineStr"/>
-      <c r="K28" s="5" t="inlineStr"/>
+      <c r="C28" s="5" t="n">
+        <v>0.4717244611274124</v>
+      </c>
+      <c r="D28" s="5" t="n">
+        <v>0.5336093039181672</v>
+      </c>
+      <c r="E28" s="5" t="n">
+        <v>-2.589914108329572</v>
+      </c>
+      <c r="F28" s="5" t="n">
+        <v>0.2853893729540063</v>
+      </c>
+      <c r="G28" s="5" t="n">
+        <v>-1.01485950858673</v>
+      </c>
+      <c r="H28" s="5" t="n">
+        <v>0.2890426751981395</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="n"/>
@@ -1072,15 +1266,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C29" s="5" t="inlineStr"/>
-      <c r="D29" s="5" t="inlineStr"/>
-      <c r="E29" s="5" t="inlineStr"/>
-      <c r="F29" s="5" t="inlineStr"/>
-      <c r="G29" s="5" t="inlineStr"/>
-      <c r="H29" s="5" t="inlineStr"/>
-      <c r="I29" s="5" t="inlineStr"/>
-      <c r="J29" s="5" t="inlineStr"/>
-      <c r="K29" s="5" t="inlineStr"/>
+      <c r="C29" s="5" t="n">
+        <v>-3.578391554431874</v>
+      </c>
+      <c r="D29" s="5" t="n">
+        <v>-5.526939977389569</v>
+      </c>
+      <c r="E29" s="5" t="n">
+        <v>-6.444345441061502</v>
+      </c>
+      <c r="F29" s="5" t="n">
+        <v>-6.710815629198954</v>
+      </c>
+      <c r="G29" s="5" t="n">
+        <v>-3.442829150664457</v>
+      </c>
+      <c r="H29" s="5" t="n">
+        <v>-4.793972724260152</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="n"/>
@@ -1089,15 +1292,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C30" s="5" t="inlineStr"/>
-      <c r="D30" s="5" t="inlineStr"/>
-      <c r="E30" s="5" t="inlineStr"/>
-      <c r="F30" s="5" t="inlineStr"/>
-      <c r="G30" s="5" t="inlineStr"/>
-      <c r="H30" s="5" t="inlineStr"/>
-      <c r="I30" s="5" t="inlineStr"/>
-      <c r="J30" s="5" t="inlineStr"/>
-      <c r="K30" s="5" t="inlineStr"/>
+      <c r="C30" s="5" t="n">
+        <v>3.698507134365541</v>
+      </c>
+      <c r="D30" s="5" t="n">
+        <v>7.416754664473493</v>
+      </c>
+      <c r="E30" s="5" t="n">
+        <v>1.067464307569909</v>
+      </c>
+      <c r="F30" s="5" t="n">
+        <v>8.735037053916413</v>
+      </c>
+      <c r="G30" s="5" t="n">
+        <v>1.690514789592272</v>
+      </c>
+      <c r="H30" s="5" t="n">
+        <v>6.027987462507171</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="n"/>
@@ -1106,15 +1318,24 @@
           <t>Cambio relativo (%)</t>
         </is>
       </c>
-      <c r="C31" s="6" t="inlineStr"/>
-      <c r="D31" s="6" t="inlineStr"/>
-      <c r="E31" s="6" t="inlineStr"/>
-      <c r="F31" s="6" t="inlineStr"/>
-      <c r="G31" s="6" t="inlineStr"/>
-      <c r="H31" s="6" t="inlineStr"/>
-      <c r="I31" s="6" t="inlineStr"/>
-      <c r="J31" s="6" t="inlineStr"/>
-      <c r="K31" s="6" t="inlineStr"/>
+      <c r="C31" s="6" t="n">
+        <v>0.02473756379704759</v>
+      </c>
+      <c r="D31" s="6" t="n">
+        <v>0.02798284864606259</v>
+      </c>
+      <c r="E31" s="6" t="n">
+        <v>-0.1206340374731562</v>
+      </c>
+      <c r="F31" s="6" t="n">
+        <v>0.01329297840443794</v>
+      </c>
+      <c r="G31" s="6" t="n">
+        <v>-0.05015895757214219</v>
+      </c>
+      <c r="H31" s="6" t="n">
+        <v>0.01428579932407753</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="n"/>
@@ -1123,15 +1344,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C32" s="6" t="inlineStr"/>
-      <c r="D32" s="6" t="inlineStr"/>
-      <c r="E32" s="6" t="inlineStr"/>
-      <c r="F32" s="6" t="inlineStr"/>
-      <c r="G32" s="6" t="inlineStr"/>
-      <c r="H32" s="6" t="inlineStr"/>
-      <c r="I32" s="6" t="inlineStr"/>
-      <c r="J32" s="6" t="inlineStr"/>
-      <c r="K32" s="6" t="inlineStr"/>
+      <c r="C32" s="6" t="n">
+        <v>-0.1695574084003518</v>
+      </c>
+      <c r="D32" s="6" t="n">
+        <v>-0.2842942592823844</v>
+      </c>
+      <c r="E32" s="6" t="n">
+        <v>-0.2737824502643383</v>
+      </c>
+      <c r="F32" s="6" t="n">
+        <v>-0.2992441296674267</v>
+      </c>
+      <c r="G32" s="6" t="n">
+        <v>-0.1641393401089721</v>
+      </c>
+      <c r="H32" s="6" t="n">
+        <v>-0.2297462831859447</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="n"/>
@@ -1140,15 +1370,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C33" s="6" t="inlineStr"/>
-      <c r="D33" s="6" t="inlineStr"/>
-      <c r="E33" s="6" t="inlineStr"/>
-      <c r="F33" s="6" t="inlineStr"/>
-      <c r="G33" s="6" t="inlineStr"/>
-      <c r="H33" s="6" t="inlineStr"/>
-      <c r="I33" s="6" t="inlineStr"/>
-      <c r="J33" s="6" t="inlineStr"/>
-      <c r="K33" s="6" t="inlineStr"/>
+      <c r="C33" s="6" t="n">
+        <v>0.2137743534288248</v>
+      </c>
+      <c r="D33" s="6" t="n">
+        <v>0.411839324839674</v>
+      </c>
+      <c r="E33" s="6" t="n">
+        <v>0.05354844655965096</v>
+      </c>
+      <c r="F33" s="6" t="n">
+        <v>0.4192858127940617</v>
+      </c>
+      <c r="G33" s="6" t="n">
+        <v>0.08697968959025323</v>
+      </c>
+      <c r="H33" s="6" t="n">
+        <v>0.3178042461548923</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1159,11 +1398,11 @@
     </row>
   </sheetData>
   <mergeCells count="9">
-    <mergeCell ref="C1:E1"/>
     <mergeCell ref="A22:A27"/>
     <mergeCell ref="A4:A9"/>
-    <mergeCell ref="F1:H1"/>
-    <mergeCell ref="I1:K1"/>
+    <mergeCell ref="C1:D1"/>
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="E1:F1"/>
     <mergeCell ref="A16:A21"/>
     <mergeCell ref="A10:A15"/>
     <mergeCell ref="A28:A33"/>
